--- a/data/obx_xlsx/HAFNI.OL.xlsx
+++ b/data/obx_xlsx/HAFNI.OL.xlsx
@@ -7336,11 +7336,21 @@
       <c r="I46" s="16">
         <v>9077.54</v>
       </c>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="15"/>
+      <c r="J46" s="16">
+        <v>8321.54</v>
+      </c>
+      <c r="K46" s="16">
+        <v>7471.8</v>
+      </c>
+      <c r="L46" s="16">
+        <v>3528.67</v>
+      </c>
+      <c r="M46" s="16">
+        <v>1595.89</v>
+      </c>
+      <c r="N46" s="16">
+        <v>1019.53</v>
+      </c>
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
@@ -8383,11 +8393,21 @@
       <c r="D80" s="16">
         <v>1016.95</v>
       </c>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="15"/>
-      <c r="H80" s="15"/>
-      <c r="I80" s="15"/>
+      <c r="E80" s="16">
+        <v>1738.01</v>
+      </c>
+      <c r="F80" s="16">
+        <v>1226.11</v>
+      </c>
+      <c r="G80" s="16">
+        <v>1547.32</v>
+      </c>
+      <c r="H80" s="16">
+        <v>664.66</v>
+      </c>
+      <c r="I80" s="16">
+        <v>1293.71</v>
+      </c>
       <c r="J80" s="16">
         <v>412.1</v>
       </c>
